--- a/template/wif_workbook.xlsx
+++ b/template/wif_workbook.xlsx
@@ -479,7 +479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A53"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="116" customWidth="1" min="1" max="1"/>
@@ -578,259 +578,308 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  verb       SET / JOIN / FILTER / APPEND / REPLACE / CODE / LET (reference below).</t>
+          <t xml:space="preserve">  verb       SET / JOIN / FILTER / APPEND / REPLACE / CODE / ASSERT / SAVE /</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  target     usually BLANK = the hooked table itself. INPUT rules need libref.table.</t>
+          <t xml:space="preserve">             SORT / DEDUPE / LET (reference below).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  where_clause  row condition. SET/JOIN: IF syntax (in, =:, missing(), date literals);</t>
+          <t xml:space="preserve">  target     usually BLANK = the hooked table itself. INPUT rules need libref.table.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">             FILTER/APPEND: full WHERE syntax (LIKE, BETWEEN, IS MISSING ...).</t>
+          <t xml:space="preserve">  where_clause  row condition. SET/JOIN: IF syntax (in, =:, missing(), date literals);</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  keys       JOIN only: space-separated key columns (same names both sides).</t>
+          <t xml:space="preserve">             FILTER/APPEND: full WHERE syntax (LIKE, BETWEEN, IS MISSING ...).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  source     JOIN/APPEND/REPLACE: the lookup/donor table (WORK.X or libref.X).</t>
+          <t xml:space="preserve">  keys       JOIN only: space-separated key columns (same names both sides).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  columns    JOIN/APPEND/REPLACE column mapping: srccol or srccol=targetcol, spaces</t>
+          <t xml:space="preserve">  source     JOIN/APPEND/REPLACE: the lookup/donor table (WORK.X or libref.X).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">             between. JOIN with columns blank = update same-named columns.</t>
+          <t xml:space="preserve">  columns    JOIN/APPEND/REPLACE column mapping: srccol or srccol=targetcol, spaces</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  assign     SET/JOIN: SAS assignment statements. CODE: the code. LET: the value.</t>
+          <t xml:space="preserve">             between. JOIN with columns blank = update same-named columns.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  options    ONCE  ITERS=1|2+|ALL  NEWCOLS  NOWARN0  DROP  KEEPEXTRA  ALLOWLIB</t>
+          <t xml:space="preserve">  assign     SET/JOIN: SAS assignment statements. CODE: the code. LET: the value.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  options    ONCE  ITERS=1|2+|ALL  NEWCOLS  NOWARN0  DROP  KEEPEXTRA  ALLOWLIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">             LAST (DEDUPE)  NOMATCH=KEEP|FAIL|DELETE (JOIN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  notes      free text for humans.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Verb reference</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  SET      change columns in place:  assign 'policy_age = policy_age + 1;'</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  JOIN     the workhorse: hash left-join source by keys; matched rows can pull columns</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">           (columns cell) AND compute (assign cell: 'rate = rate * adj_factor;').</t>
+          <t xml:space="preserve">  SET      change columns in place:  assign 'policy_age = policy_age + 1;'</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">           Unmatched rows are untouched; duplicate source keys are a hard error.</t>
+          <t xml:space="preserve">  JOIN     the workhorse: hash left-join source by keys; matched rows can pull columns</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FILTER   keep rows matching where_clause (options DROP inverts).</t>
+          <t xml:space="preserve">           (columns cell) AND compute (assign cell: 'rate = rate * adj_factor;').</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  APPEND   add the source's rows (where_clause filters the SOURCE).</t>
+          <t xml:space="preserve">           Unmatched rows are untouched; duplicate source keys are a hard error.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  REPLACE  swap the whole table for the source (trimmed to the target's columns</t>
+          <t xml:space="preserve">  FILTER   keep rows matching where_clause (options DROP inverts).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">           unless KEEPEXTRA).</t>
+          <t xml:space="preserve">  APPEND   add the source's rows (where_clause filters the SOURCE).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  CODE     escape hatch: the assign cell is inlined verbatim as generated code.</t>
+          <t xml:space="preserve">  REPLACE  swap the whole table for the source (trimmed to the target's columns</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">           You may reference the live built-ins WIF_TABLE / WIF_HOOK there.</t>
+          <t xml:space="preserve">           unless KEEPEXTRA).</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  LET      define a parameter: target = its name, assign = its value. Rows with a</t>
+          <t xml:space="preserve">  ASSERT   QA gate, never modifies: where_clause = the condition EVERY row must</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">           scenario override global rows of the same name. Reference as &amp;NAME.</t>
+          <t xml:space="preserve">           satisfy (full WHERE). Violations -&gt; FAILED + sample in work.wif_viol.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr"/>
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SAVE     snapshot the hooked table; the DESTINATION goes in the source column</t>
+        </is>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Cell rules (the lint enforces all of these before anything runs)</t>
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">           (parameters fine: RESULTS.SNAP_&amp;WIF_SCENARIO.).</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Text literals in single quotes: region = 'EAST', dates '01JAN2027'd.</t>
+          <t xml:space="preserve">  SORT     keys with DESCENDING allowed.   DEDUPE  keep FIRST (or LAST) per keys.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Ampersand / percent inside single quotes is fine ('R&amp;D', '5%').</t>
+          <t xml:space="preserve">  CODE     escape hatch: the assign cell is inlined verbatim as generated code.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * &amp;NAME outside quotes must be a LET parameter, params= value, or a built-in</t>
+          <t xml:space="preserve">           You may reference the live built-ins WIF_TABLE / WIF_HOOK there.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    (&amp;WIF_ITER, &amp;WIF_SCENARIO; &amp;WIF_TABLE / &amp;WIF_HOOK inside CODE cells).</t>
+          <t xml:space="preserve">  LET      define a parameter: target = its name, assign = its value. Rows with a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * No /* comments in cells - use notes. Keep expression columns Text-formatted.</t>
+          <t xml:space="preserve">           scenario override global rows of the same name. Reference as &amp;NAME.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  * A row whose scenario or hook cell starts with # is a comment row.</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr"/>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Cell rules (the lint enforces all of these before anything runs)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>Remember</t>
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Text literals in single quotes: region = 'EAST', dates '01JAN2027'd.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * Hooks are inert until %wif_init runs - safe to leave in the program permanently.</t>
+          <t xml:space="preserve">  * Ampersand / percent inside single quotes is fine ('R&amp;D', '5%').</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * INPUT rules stage modified copies under WORK; your base folder stays pristine.</t>
+          <t xml:space="preserve">  * &amp;NAME outside quotes must be a LET parameter, params= value, or a built-in</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  * work.wif_log records every rule application (rows before/after/affected).</t>
+          <t xml:space="preserve">    (&amp;WIF_ITER, &amp;WIF_SCENARIO; &amp;WIF_TABLE / &amp;WIF_HOOK inside CODE cells).</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * No /* comments in cells - use notes. Keep expression columns Text-formatted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * A row whose scenario or hook cell starts with # is a comment row.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>Remember</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * Hooks are inert until %wif_init runs - safe to leave in the program permanently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * INPUT rules stage modified copies under WORK; your base folder stays pristine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  * work.wif_log records every rule application (rows before/after/affected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">  * Save this workbook where the SAS SERVER can read it (EG users: server path!).</t>
         </is>
@@ -8124,7 +8173,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SET,JOIN,FILTER,APPEND,REPLACE,CODE,LET"</formula1>
+      <formula1>"SET,JOIN,FILTER,APPEND,REPLACE,CODE,ASSERT,SAVE,SORT,DEDUPE,LET"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Y,N"</formula1>
